--- a/premuim.xlsx
+++ b/premuim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ROYAN\Desktop\b2b-platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9518D4E2-E6D2-486D-A989-33B6053A9923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D968C9E2-B87E-4448-B905-407484E73F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,9 +102,6 @@
     <t>۶ بار در ماه + اولویت بالاتر</t>
   </si>
   <si>
-    <t>قرار دادن محصولات در فهرست محصولات برتر</t>
-  </si>
-  <si>
     <t>قرار گرفتن در بالای نتایج جستجو</t>
   </si>
   <si>
@@ -211,6 +208,9 @@
   </si>
   <si>
     <t>busines</t>
+  </si>
+  <si>
+    <t>قرار دادن محصولات در فهرست محصولات برتر(انتخاب 3 محصول)</t>
   </si>
 </sst>
 </file>
@@ -218,12 +218,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="[$-3000401]0"/>
+    <numFmt numFmtId="164" formatCode="[$-3000401]0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -267,10 +282,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -284,14 +300,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -580,7 +606,7 @@
     <col min="13" max="16384" width="13.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -594,10 +620,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -614,7 +640,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -631,7 +657,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -647,8 +673,10 @@
       <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -664,8 +692,9 @@
       <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
@@ -682,7 +711,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
@@ -698,10 +727,11 @@
       <c r="E7" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="9"/>
+    </row>
+    <row r="8" spans="1:8" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -716,111 +746,111 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="4" t="s">
+    </row>
+    <row r="11" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="B13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="B15" s="5">
         <v>2</v>
@@ -835,9 +865,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>17</v>
@@ -854,7 +884,7 @@
     </row>
     <row r="17" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>17</v>
@@ -871,19 +901,19 @@
     </row>
     <row r="18" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -891,21 +921,21 @@
         <v>5</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>17</v>
@@ -917,46 +947,46 @@
         <v>23</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="E21" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="E22" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>17</v>
@@ -973,7 +1003,7 @@
     </row>
     <row r="24" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>17</v>
